--- a/data/trans_orig/P6701-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P6701-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27285</t>
+          <t>27005</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51614</t>
+          <t>51859</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19910</t>
+          <t>19774</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40931</t>
+          <t>41451</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52398</t>
+          <t>52873</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85372</t>
+          <t>84138</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,92%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23768</t>
+          <t>22318</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46485</t>
+          <t>44569</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19957</t>
+          <t>20848</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42270</t>
+          <t>42465</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47747</t>
+          <t>47263</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>78438</t>
+          <t>77436</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,57%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>109461</t>
+          <t>112756</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>148081</t>
+          <t>147887</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>56002</t>
+          <t>56560</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>82866</t>
+          <t>83774</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>177892</t>
+          <t>175137</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>224523</t>
+          <t>220103</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>44,27%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>49862</t>
+          <t>50070</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>79989</t>
+          <t>79893</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24888</t>
+          <t>24689</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48752</t>
+          <t>48475</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>79356</t>
+          <t>83126</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>118272</t>
+          <t>119000</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,93%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27939</t>
+          <t>29557</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52417</t>
+          <t>54709</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21605</t>
+          <t>20967</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43187</t>
+          <t>41210</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>54742</t>
+          <t>54550</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>87074</t>
+          <t>87369</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,57%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13614</t>
+          <t>13151</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34842</t>
+          <t>35047</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5188</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19137</t>
+          <t>21644</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22854</t>
+          <t>23212</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49450</t>
+          <t>47986</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23534</t>
+          <t>22796</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47301</t>
+          <t>46882</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17580</t>
+          <t>17382</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37135</t>
+          <t>36178</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>45675</t>
+          <t>44288</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>76765</t>
+          <t>75741</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>82926</t>
+          <t>81596</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>117257</t>
+          <t>115209</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>54865</t>
+          <t>55028</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>82548</t>
+          <t>81782</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>147087</t>
+          <t>148401</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>189517</t>
+          <t>191104</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>45,01%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42567</t>
+          <t>41991</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>70651</t>
+          <t>70344</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22344</t>
+          <t>21617</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42919</t>
+          <t>42726</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>68904</t>
+          <t>70939</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>105946</t>
+          <t>106665</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,12%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34726</t>
+          <t>34873</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>59071</t>
+          <t>60739</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21000</t>
+          <t>21117</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43233</t>
+          <t>43874</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>61507</t>
+          <t>62084</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>93341</t>
+          <t>93799</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,09%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10423</t>
+          <t>10619</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28037</t>
+          <t>26706</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3938</t>
+          <t>4771</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15278</t>
+          <t>15895</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17194</t>
+          <t>18111</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36475</t>
+          <t>37531</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22120</t>
+          <t>20285</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44369</t>
+          <t>42788</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10874</t>
+          <t>11206</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25881</t>
+          <t>26584</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36426</t>
+          <t>36969</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>63417</t>
+          <t>63431</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,17%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>90253</t>
+          <t>91839</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>123682</t>
+          <t>125360</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>29597</t>
+          <t>29432</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>49502</t>
+          <t>49465</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>126686</t>
+          <t>128147</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>165137</t>
+          <t>165304</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>42,13%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>63328</t>
+          <t>62342</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>93027</t>
+          <t>92627</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15901</t>
+          <t>15942</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33938</t>
+          <t>34686</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>85149</t>
+          <t>85380</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>119688</t>
+          <t>119438</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,44%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34963</t>
+          <t>36074</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>61723</t>
+          <t>62304</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,47 +2563,47 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>12,86%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>22,2%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>21596</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>13928</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>30526</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>19,32%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
           <t>12,46%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>22,0%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>21596</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>14330</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>31452</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>19,32%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>12,82%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>54984</t>
+          <t>55779</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>86742</t>
+          <t>86864</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,14%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31492</t>
+          <t>32004</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>60027</t>
+          <t>58827</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31500</t>
+          <t>31403</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>57842</t>
+          <t>56879</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>70429</t>
+          <t>68760</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>108951</t>
+          <t>105679</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,54%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>33514</t>
+          <t>34556</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>62548</t>
+          <t>61250</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>15239</t>
+          <t>15051</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>33458</t>
+          <t>33948</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>54236</t>
+          <t>54588</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>88485</t>
+          <t>87354</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,02%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>129774</t>
+          <t>128924</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>170719</t>
+          <t>173688</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>81297</t>
+          <t>82764</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>115443</t>
+          <t>116459</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>221029</t>
+          <t>222490</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>275412</t>
+          <t>275618</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,93%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>86160</t>
+          <t>84823</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>120684</t>
+          <t>121943</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>57065</t>
+          <t>55724</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>85064</t>
+          <t>86986</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>150625</t>
+          <t>148794</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>197217</t>
+          <t>196826</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,08%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>66543</t>
+          <t>66620</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>101329</t>
+          <t>101104</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>51550</t>
+          <t>50833</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>81708</t>
+          <t>81441</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>128419</t>
+          <t>126955</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>174477</t>
+          <t>172279</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>23,71%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10122</t>
+          <t>9136</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13979</t>
+          <t>13304</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>33507</t>
+          <t>32028</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>16976</t>
+          <t>17563</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>37124</t>
+          <t>37700</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,48%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3814</t>
+          <t>3824</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14912</t>
+          <t>15278</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>18132</t>
+          <t>18223</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>11300</t>
+          <t>11664</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>28586</t>
+          <t>28171</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>39089</t>
+          <t>38935</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>63169</t>
+          <t>62651</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>38153</t>
+          <t>37978</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>62333</t>
+          <t>62488</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>84921</t>
+          <t>84481</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>120603</t>
+          <t>118944</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,21%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>31464</t>
+          <t>30590</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>54911</t>
+          <t>53220</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>34675</t>
+          <t>34499</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>58608</t>
+          <t>58873</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>72238</t>
+          <t>71697</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>104344</t>
+          <t>105460</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>32,1%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>37007</t>
+          <t>38063</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>60187</t>
+          <t>61393</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>35695</t>
+          <t>35546</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>60161</t>
+          <t>60022</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>79187</t>
+          <t>78416</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>113076</t>
+          <t>112052</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,11%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>106177</t>
+          <t>104603</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>150835</t>
+          <t>151165</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>94723</t>
+          <t>94780</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>136221</t>
+          <t>136144</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>213087</t>
+          <t>212573</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>273213</t>
+          <t>272587</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>128311</t>
+          <t>128544</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>177233</t>
+          <t>178218</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>87675</t>
+          <t>89267</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>127143</t>
+          <t>129341</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>230390</t>
+          <t>227321</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>292399</t>
+          <t>287794</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,15%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>498003</t>
+          <t>500950</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>575729</t>
+          <t>576113</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>294209</t>
+          <t>296644</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>354222</t>
+          <t>355599</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>814509</t>
+          <t>816880</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>913659</t>
+          <t>914399</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,59%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>311380</t>
+          <t>310238</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>375891</t>
+          <t>374984</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>181745</t>
+          <t>181522</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>233995</t>
+          <t>235308</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>502125</t>
+          <t>505461</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>589543</t>
+          <t>586225</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,74%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>237949</t>
+          <t>240442</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>297914</t>
+          <t>299735</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>170509</t>
+          <t>169347</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>220108</t>
+          <t>220713</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>417124</t>
+          <t>421489</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>499761</t>
+          <t>495878</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,93%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20295</t>
+          <t>19470</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43039</t>
+          <t>41473</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14420</t>
+          <t>14617</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33797</t>
+          <t>32794</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39526</t>
+          <t>40542</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67948</t>
+          <t>67978</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43002</t>
+          <t>42511</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>70447</t>
+          <t>67925</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25270</t>
+          <t>26169</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48133</t>
+          <t>48515</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>72750</t>
+          <t>73709</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>109750</t>
+          <t>108919</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,12%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>99077</t>
+          <t>97874</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>132528</t>
+          <t>132270</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>70593</t>
+          <t>70539</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>99669</t>
+          <t>98699</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>176853</t>
+          <t>177010</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>222330</t>
+          <t>222503</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>45,18%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34420</t>
+          <t>34797</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59611</t>
+          <t>59962</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28713</t>
+          <t>28187</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50867</t>
+          <t>51235</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>67834</t>
+          <t>67851</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>101893</t>
+          <t>102639</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,84%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>22325</t>
+          <t>22870</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45172</t>
+          <t>45838</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22887</t>
+          <t>23043</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>44795</t>
+          <t>43906</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>51059</t>
+          <t>50265</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>84245</t>
+          <t>83027</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,86%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9676</t>
+          <t>10035</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26666</t>
+          <t>27038</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6554</t>
+          <t>6809</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20323</t>
+          <t>20929</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19172</t>
+          <t>19395</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41490</t>
+          <t>41246</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21697</t>
+          <t>21350</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43563</t>
+          <t>44228</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23614</t>
+          <t>23396</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44255</t>
+          <t>44631</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>50153</t>
+          <t>50371</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>80391</t>
+          <t>79659</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,39%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>79102</t>
+          <t>77904</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>110578</t>
+          <t>108602</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>56352</t>
+          <t>55425</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>79985</t>
+          <t>81314</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>138947</t>
+          <t>139197</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>182601</t>
+          <t>181199</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>41,83%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41794</t>
+          <t>41553</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69092</t>
+          <t>67445</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38970</t>
+          <t>36781</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61912</t>
+          <t>62377</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>85459</t>
+          <t>86446</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>124168</t>
+          <t>122394</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,25%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34700</t>
+          <t>35589</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62752</t>
+          <t>63545</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18577</t>
+          <t>18239</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>38499</t>
+          <t>37072</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>58929</t>
+          <t>60116</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>91838</t>
+          <t>93416</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,56%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3549</t>
+          <t>3551</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15990</t>
+          <t>15859</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2491</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7313</t>
+          <t>6976</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22408</t>
+          <t>22561</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17218</t>
+          <t>17983</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37085</t>
+          <t>38886</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4235</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16370</t>
+          <t>15940</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25367</t>
+          <t>25249</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>49578</t>
+          <t>48772</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,15%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>60518</t>
+          <t>60923</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>88138</t>
+          <t>89144</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>23012</t>
+          <t>22877</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>39016</t>
+          <t>38478</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>90301</t>
+          <t>88034</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>122925</t>
+          <t>121857</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>42,84%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>65576</t>
+          <t>66675</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>93091</t>
+          <t>96429</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7383</t>
+          <t>7093</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20753</t>
+          <t>20299</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>77275</t>
+          <t>76332</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>109549</t>
+          <t>108073</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>37,99%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19812</t>
+          <t>20083</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>40633</t>
+          <t>40887</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4310</t>
+          <t>3988</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15944</t>
+          <t>15892</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>27853</t>
+          <t>27614</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>49544</t>
+          <t>52263</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>18,37%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28057</t>
+          <t>28537</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52813</t>
+          <t>53321</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22233</t>
+          <t>21924</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44383</t>
+          <t>42970</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>54540</t>
+          <t>57008</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>88106</t>
+          <t>88988</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>33194</t>
+          <t>33846</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>59771</t>
+          <t>59708</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>27394</t>
+          <t>27438</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>51630</t>
+          <t>50981</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>65991</t>
+          <t>67757</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>101534</t>
+          <t>102193</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,93%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>123125</t>
+          <t>123405</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>161917</t>
+          <t>163233</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>114118</t>
+          <t>115095</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>151483</t>
+          <t>152973</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>247538</t>
+          <t>250144</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>302918</t>
+          <t>302937</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>141147</t>
+          <t>139475</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>182349</t>
+          <t>181487</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>68221</t>
+          <t>69602</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>100922</t>
+          <t>101821</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>218239</t>
+          <t>217597</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>272829</t>
+          <t>270118</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,53%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>85272</t>
+          <t>85026</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>121210</t>
+          <t>122812</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>65107</t>
+          <t>66530</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>98665</t>
+          <t>98412</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>161013</t>
+          <t>159959</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>208627</t>
+          <t>207077</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,17%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8473</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7994</t>
+          <t>8060</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>22414</t>
+          <t>23715</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>10293</t>
+          <t>9946</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>26428</t>
+          <t>27085</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -7898,12 +7898,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6317</t>
+          <t>6150</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>19309</t>
+          <t>20086</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7913,12 +7913,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7933,12 +7933,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>11792</t>
+          <t>11405</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>27479</t>
+          <t>29617</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7948,12 +7948,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7968,12 +7968,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>21390</t>
+          <t>20716</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>42562</t>
+          <t>42243</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7983,12 +7983,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>66708</t>
+          <t>65971</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>93552</t>
+          <t>93199</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8026,12 +8026,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8046,12 +8046,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>62604</t>
+          <t>63556</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>89210</t>
+          <t>90305</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8081,12 +8081,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>136993</t>
+          <t>134994</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>175614</t>
+          <t>175154</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,73%</t>
         </is>
       </c>
     </row>
@@ -8124,12 +8124,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>43060</t>
+          <t>44877</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>69243</t>
+          <t>70203</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8139,12 +8139,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8159,12 +8159,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>41562</t>
+          <t>40168</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>66738</t>
+          <t>64701</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8194,12 +8194,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>91975</t>
+          <t>91456</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>126150</t>
+          <t>130181</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>33,24%</t>
         </is>
       </c>
     </row>
@@ -8237,12 +8237,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>31681</t>
+          <t>32863</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>55377</t>
+          <t>56389</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8252,12 +8252,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8272,12 +8272,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>26421</t>
+          <t>27400</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>48212</t>
+          <t>49180</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8287,12 +8287,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8307,12 +8307,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>64554</t>
+          <t>64961</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>98576</t>
+          <t>96705</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8322,12 +8322,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>24,7%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>77716</t>
+          <t>77469</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>118542</t>
+          <t>116248</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>69750</t>
+          <t>68020</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>105094</t>
+          <t>103209</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>158020</t>
+          <t>156955</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>209931</t>
+          <t>209560</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -8580,12 +8580,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>145913</t>
+          <t>145513</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>194805</t>
+          <t>194376</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8595,12 +8595,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8615,12 +8615,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>111890</t>
+          <t>111781</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>155728</t>
+          <t>156485</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8630,12 +8630,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8650,12 +8650,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>272936</t>
+          <t>270625</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>338413</t>
+          <t>337941</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8665,12 +8665,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -8693,12 +8693,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>469472</t>
+          <t>471053</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>540658</t>
+          <t>544442</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8728,12 +8728,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>361276</t>
+          <t>361749</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>426336</t>
+          <t>424577</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8743,12 +8743,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>849598</t>
+          <t>848082</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>953534</t>
+          <t>945941</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8778,12 +8778,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>38,48%</t>
         </is>
       </c>
     </row>
@@ -8806,12 +8806,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>363718</t>
+          <t>361140</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>431612</t>
+          <t>430832</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8841,12 +8841,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>210588</t>
+          <t>212335</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>264940</t>
+          <t>267206</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8856,12 +8856,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8876,12 +8876,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>584980</t>
+          <t>590733</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>674600</t>
+          <t>676372</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8891,12 +8891,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,51%</t>
         </is>
       </c>
     </row>
@@ -8919,12 +8919,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>226109</t>
+          <t>226467</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>286593</t>
+          <t>289912</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8954,12 +8954,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>163254</t>
+          <t>161353</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>213039</t>
+          <t>211828</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8969,12 +8969,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -8989,12 +8989,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>403616</t>
+          <t>403914</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>481010</t>
+          <t>481260</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9004,12 +9004,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,58%</t>
         </is>
       </c>
     </row>
@@ -9377,32 +9377,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>33630</t>
+          <t>37451</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24269</t>
+          <t>27068</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42791</t>
+          <t>49357</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9412,32 +9412,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>25560</t>
+          <t>26682</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18945</t>
+          <t>19335</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34189</t>
+          <t>35121</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9447,32 +9447,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>59189</t>
+          <t>64133</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47768</t>
+          <t>50429</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>71848</t>
+          <t>79147</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>42,35%</t>
         </is>
       </c>
     </row>
@@ -9490,32 +9490,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11046</t>
+          <t>12770</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5656</t>
+          <t>6615</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20776</t>
+          <t>22732</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9525,32 +9525,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14695</t>
+          <t>16255</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9798</t>
+          <t>10172</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21614</t>
+          <t>23261</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9560,32 +9560,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>25741</t>
+          <t>29025</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18434</t>
+          <t>19920</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37518</t>
+          <t>41248</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,07%</t>
         </is>
       </c>
     </row>
@@ -9603,32 +9603,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20359</t>
+          <t>23298</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12481</t>
+          <t>13903</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31485</t>
+          <t>34546</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9638,32 +9638,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>24791</t>
+          <t>25828</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17633</t>
+          <t>19353</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32621</t>
+          <t>34540</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9673,32 +9673,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>45150</t>
+          <t>49126</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>33974</t>
+          <t>37756</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>56954</t>
+          <t>62403</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,39%</t>
         </is>
       </c>
     </row>
@@ -9716,32 +9716,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14412</t>
+          <t>16125</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8521</t>
+          <t>8922</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23029</t>
+          <t>24676</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9751,32 +9751,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>11418</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5929</t>
+          <t>6817</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16670</t>
+          <t>17420</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9786,32 +9786,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>24730</t>
+          <t>27543</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16861</t>
+          <t>18968</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34453</t>
+          <t>37992</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,33%</t>
         </is>
       </c>
     </row>
@@ -9829,32 +9829,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9550</t>
+          <t>10362</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4806</t>
+          <t>4673</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17100</t>
+          <t>18991</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9864,32 +9864,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6468</t>
+          <t>6712</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2736</t>
+          <t>3169</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12164</t>
+          <t>13381</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9899,32 +9899,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>16018</t>
+          <t>17074</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9651</t>
+          <t>9947</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>26309</t>
+          <t>27839</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>14,9%</t>
         </is>
       </c>
     </row>
@@ -9942,17 +9942,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88998</t>
+          <t>100006</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88998</t>
+          <t>100006</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88998</t>
+          <t>100006</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9977,17 +9977,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>81831</t>
+          <t>86895</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>81831</t>
+          <t>86895</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>81831</t>
+          <t>86895</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10012,17 +10012,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>170828</t>
+          <t>186902</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>170828</t>
+          <t>186902</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>170828</t>
+          <t>186902</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10059,32 +10059,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13086</t>
+          <t>15537</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6977</t>
+          <t>8884</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20629</t>
+          <t>23147</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10094,32 +10094,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11990</t>
+          <t>14455</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7144</t>
+          <t>8911</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18045</t>
+          <t>21449</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10129,32 +10129,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>25076</t>
+          <t>29993</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17117</t>
+          <t>21419</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34492</t>
+          <t>41898</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>29,58%</t>
         </is>
       </c>
     </row>
@@ -10172,32 +10172,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5493</t>
+          <t>5497</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2133</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11820</t>
+          <t>12123</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10207,32 +10207,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10966</t>
+          <t>10610</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>6155</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18187</t>
+          <t>18154</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10242,32 +10242,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>16459</t>
+          <t>16107</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9831</t>
+          <t>9859</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>25146</t>
+          <t>25343</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -10285,32 +10285,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>30563</t>
+          <t>31407</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22895</t>
+          <t>22897</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39470</t>
+          <t>40472</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10320,32 +10320,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18841</t>
+          <t>19548</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13324</t>
+          <t>13747</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25242</t>
+          <t>26034</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10355,32 +10355,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>49404</t>
+          <t>50955</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>39201</t>
+          <t>38796</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>60641</t>
+          <t>62116</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>43,85%</t>
         </is>
       </c>
     </row>
@@ -10398,32 +10398,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16527</t>
+          <t>18255</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9888</t>
+          <t>11164</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25652</t>
+          <t>28100</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10433,32 +10433,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13863</t>
+          <t>15650</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8305</t>
+          <t>9831</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20722</t>
+          <t>22527</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10468,32 +10468,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>30391</t>
+          <t>33905</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21275</t>
+          <t>24148</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41208</t>
+          <t>45626</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>32,21%</t>
         </is>
       </c>
     </row>
@@ -10511,32 +10511,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3446</t>
+          <t>3681</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>934</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10546,32 +10546,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>6351</t>
+          <t>7009</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>3138</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12421</t>
+          <t>13317</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10581,32 +10581,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>9797</t>
+          <t>10691</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4814</t>
+          <t>5283</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17878</t>
+          <t>18299</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>12,92%</t>
         </is>
       </c>
     </row>
@@ -10624,17 +10624,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>69115</t>
+          <t>74377</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69115</t>
+          <t>74377</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>69115</t>
+          <t>74377</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10659,17 +10659,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>62011</t>
+          <t>67273</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>62011</t>
+          <t>67273</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>62011</t>
+          <t>67273</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10694,17 +10694,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>131126</t>
+          <t>141650</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>131126</t>
+          <t>141650</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>131126</t>
+          <t>141650</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10741,32 +10741,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>254721</t>
+          <t>11679</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37020</t>
+          <t>6028</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>298593</t>
+          <t>19792</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10776,7 +10776,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>992</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -10786,12 +10786,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4130</t>
+          <t>4474</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -10801,7 +10801,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10811,32 +10811,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>255590</t>
+          <t>12671</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32552</t>
+          <t>6300</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>315637</t>
+          <t>21204</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>21,27%</t>
         </is>
       </c>
     </row>
@@ -10854,32 +10854,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6943</t>
+          <t>7197</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>3094</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38887</t>
+          <t>13745</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10889,32 +10889,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6651</t>
+          <t>7050</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3274</t>
+          <t>3270</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10873</t>
+          <t>11656</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10924,32 +10924,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>13594</t>
+          <t>14247</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2240</t>
+          <t>8423</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>56184</t>
+          <t>21768</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>21,84%</t>
         </is>
       </c>
     </row>
@@ -10967,32 +10967,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>25266</t>
+          <t>27151</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4125</t>
+          <t>17903</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>133500</t>
+          <t>37198</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11002,32 +11002,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6715</t>
+          <t>7554</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3403</t>
+          <t>4031</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11116</t>
+          <t>12792</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>31981</t>
+          <t>34705</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7600</t>
+          <t>25120</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>128037</t>
+          <t>45702</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>45,85%</t>
         </is>
       </c>
     </row>
@@ -11080,32 +11080,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>15739</t>
+          <t>17375</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2237</t>
+          <t>8942</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>89714</t>
+          <t>28106</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11115,32 +11115,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9374</t>
+          <t>11122</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5409</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14926</t>
+          <t>16950</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11150,32 +11150,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>25113</t>
+          <t>28496</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5405</t>
+          <t>18483</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>104444</t>
+          <t>40091</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>40,22%</t>
         </is>
       </c>
     </row>
@@ -11193,32 +11193,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>7425</t>
+          <t>7356</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>3065</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>44393</t>
+          <t>14646</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11228,32 +11228,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2209</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>409</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>6026</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11263,32 +11263,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>9444</t>
+          <t>9565</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>41546</t>
+          <t>17440</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>17,5%</t>
         </is>
       </c>
     </row>
@@ -11306,17 +11306,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>310094</t>
+          <t>70757</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>310094</t>
+          <t>70757</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>310094</t>
+          <t>70757</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11341,17 +11341,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25628</t>
+          <t>28928</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25628</t>
+          <t>28928</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25628</t>
+          <t>28928</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11376,17 +11376,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>335722</t>
+          <t>99685</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>335722</t>
+          <t>99685</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>335722</t>
+          <t>99685</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11423,102 +11423,102 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>15331</t>
+          <t>16431</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8627</t>
+          <t>9414</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24996</t>
+          <t>26559</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>7,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>19,75%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>9379</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>5105</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>15040</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>7,93%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>4,32%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>12,72%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>25811</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>17611</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>36951</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>10,21%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>6,97%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>20,2%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>8222</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>4679</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>14470</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>7,74%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>4,4%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>13,62%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>23553</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>15951</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>34439</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>10,24%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>6,94%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,62%</t>
         </is>
       </c>
     </row>
@@ -11536,32 +11536,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>17990</t>
+          <t>18789</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10627</t>
+          <t>11671</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>28829</t>
+          <t>30654</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11571,32 +11571,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>8051</t>
+          <t>8437</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4390</t>
+          <t>4645</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>14193</t>
+          <t>14550</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11606,32 +11606,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>26041</t>
+          <t>27227</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>16828</t>
+          <t>17930</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>37737</t>
+          <t>38344</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>15,17%</t>
         </is>
       </c>
     </row>
@@ -11649,32 +11649,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>48111</t>
+          <t>53416</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>36951</t>
+          <t>41103</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>61179</t>
+          <t>66468</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11684,32 +11684,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>38850</t>
+          <t>43841</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>30086</t>
+          <t>34476</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>48126</t>
+          <t>54760</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11719,32 +11719,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>86960</t>
+          <t>97256</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>72102</t>
+          <t>81029</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>100432</t>
+          <t>112423</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>44,48%</t>
         </is>
       </c>
     </row>
@@ -11762,32 +11762,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>26083</t>
+          <t>29007</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17494</t>
+          <t>19926</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37737</t>
+          <t>40206</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11797,32 +11797,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>29826</t>
+          <t>33339</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22684</t>
+          <t>25692</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>38883</t>
+          <t>42573</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11832,32 +11832,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>55909</t>
+          <t>62346</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>44595</t>
+          <t>49221</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>69666</t>
+          <t>77651</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,72%</t>
         </is>
       </c>
     </row>
@@ -11875,32 +11875,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>16225</t>
+          <t>16819</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8395</t>
+          <t>8720</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>28435</t>
+          <t>28536</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11910,32 +11910,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>21284</t>
+          <t>23284</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14302</t>
+          <t>16378</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>28382</t>
+          <t>31967</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11945,32 +11945,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>37509</t>
+          <t>40103</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>27475</t>
+          <t>28360</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>50938</t>
+          <t>54023</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,37%</t>
         </is>
       </c>
     </row>
@@ -11988,17 +11988,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>123741</t>
+          <t>134462</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>123741</t>
+          <t>134462</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>123741</t>
+          <t>134462</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12023,17 +12023,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>106232</t>
+          <t>118281</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>106232</t>
+          <t>118281</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>106232</t>
+          <t>118281</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12058,17 +12058,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>229973</t>
+          <t>252743</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>229973</t>
+          <t>252743</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>229973</t>
+          <t>252743</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12105,7 +12105,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>1662</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -12115,12 +12115,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5632</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -12130,7 +12130,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12140,32 +12140,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>5522</t>
+          <t>7455</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2486</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>13094</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12175,32 +12175,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7221</t>
+          <t>9117</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3630</t>
+          <t>5043</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>12272</t>
+          <t>16351</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -12218,32 +12218,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3963</t>
+          <t>4144</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11373</t>
+          <t>11142</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12253,32 +12253,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1809</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>1343</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4868</t>
+          <t>9401</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12288,32 +12288,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5772</t>
+          <t>8166</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>3515</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>13217</t>
+          <t>15301</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -12331,22 +12331,22 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>22522</t>
+          <t>27136</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>13938</t>
+          <t>18151</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>36090</t>
+          <t>38377</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -12356,7 +12356,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12366,32 +12366,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>21068</t>
+          <t>23637</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>15390</t>
+          <t>16837</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>27354</t>
+          <t>31386</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12401,32 +12401,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>43589</t>
+          <t>50773</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>33121</t>
+          <t>38521</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>59259</t>
+          <t>64124</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>35,14%</t>
         </is>
       </c>
     </row>
@@ -12444,32 +12444,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>29438</t>
+          <t>35891</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>19797</t>
+          <t>24836</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>39526</t>
+          <t>49443</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -12479,32 +12479,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>22833</t>
+          <t>26795</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>16880</t>
+          <t>19700</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>30171</t>
+          <t>35290</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -12514,32 +12514,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>52270</t>
+          <t>62686</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>40743</t>
+          <t>49263</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>64769</t>
+          <t>76184</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>41,74%</t>
         </is>
       </c>
     </row>
@@ -12557,32 +12557,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>14757</t>
+          <t>25431</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>13663</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>26257</t>
+          <t>40708</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12592,32 +12592,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>22655</t>
+          <t>26326</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>15827</t>
+          <t>18603</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>29311</t>
+          <t>34343</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12627,32 +12627,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>37412</t>
+          <t>51757</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>27991</t>
+          <t>38155</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>52190</t>
+          <t>68863</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>37,73%</t>
         </is>
       </c>
     </row>
@@ -12670,17 +12670,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>72379</t>
+          <t>94264</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>72379</t>
+          <t>94264</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>72379</t>
+          <t>94264</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12705,17 +12705,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>73886</t>
+          <t>88235</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>73886</t>
+          <t>88235</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>73886</t>
+          <t>88235</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12740,17 +12740,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>146265</t>
+          <t>182499</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>146265</t>
+          <t>182499</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>146265</t>
+          <t>182499</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12787,32 +12787,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>318468</t>
+          <t>82760</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>108981</t>
+          <t>65807</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>527709</t>
+          <t>101696</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12822,32 +12822,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>52162</t>
+          <t>58965</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>41352</t>
+          <t>45754</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>65572</t>
+          <t>73463</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12857,32 +12857,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>370630</t>
+          <t>141725</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>158754</t>
+          <t>120941</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>704802</t>
+          <t>165469</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>19,16%</t>
         </is>
       </c>
     </row>
@@ -12900,32 +12900,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>45434</t>
+          <t>48397</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>17022</t>
+          <t>34914</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>80887</t>
+          <t>66871</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12935,32 +12935,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>42173</t>
+          <t>46375</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>32405</t>
+          <t>36566</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>54055</t>
+          <t>59002</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12970,32 +12970,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>87607</t>
+          <t>94772</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>39661</t>
+          <t>76927</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>122668</t>
+          <t>115322</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>13,36%</t>
         </is>
       </c>
     </row>
@@ -13013,32 +13013,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>146821</t>
+          <t>162409</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>57811</t>
+          <t>139684</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>242474</t>
+          <t>187319</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13048,32 +13048,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>110265</t>
+          <t>120407</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>96223</t>
+          <t>103897</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>125335</t>
+          <t>137363</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13083,32 +13083,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>257085</t>
+          <t>282816</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>128150</t>
+          <t>255723</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>349777</t>
+          <t>309291</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>35,82%</t>
         </is>
       </c>
     </row>
@@ -13126,32 +13126,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>102200</t>
+          <t>116652</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>38244</t>
+          <t>96517</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>171022</t>
+          <t>138413</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13161,32 +13161,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>86213</t>
+          <t>98325</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>73077</t>
+          <t>83582</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>101944</t>
+          <t>115556</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13196,32 +13196,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>188413</t>
+          <t>214977</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>95480</t>
+          <t>188115</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>260420</t>
+          <t>242637</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>28,1%</t>
         </is>
       </c>
     </row>
@@ -13239,32 +13239,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>51403</t>
+          <t>63649</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>20647</t>
+          <t>46308</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>87276</t>
+          <t>86598</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13274,32 +13274,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>58776</t>
+          <t>65541</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>47047</t>
+          <t>51379</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>71505</t>
+          <t>80321</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13309,32 +13309,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>110179</t>
+          <t>129190</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>48730</t>
+          <t>105881</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>151927</t>
+          <t>157765</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
@@ -13352,17 +13352,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>664326</t>
+          <t>473868</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>664326</t>
+          <t>473868</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>664326</t>
+          <t>473868</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -13387,17 +13387,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>349588</t>
+          <t>389612</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>349588</t>
+          <t>389612</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>349588</t>
+          <t>389612</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -13422,17 +13422,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1013914</t>
+          <t>863480</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1013914</t>
+          <t>863480</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1013914</t>
+          <t>863480</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
